--- a/Data Files/LOS_CompanyCustomer_TestData.xlsx
+++ b/Data Files/LOS_CompanyCustomer_TestData.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Credentials" sheetId="1" state="visible" r:id="rId3"/>
@@ -2000,11 +2000,12 @@
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.09"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="6.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2986,8 +2987,10 @@
   <dimension ref="A1:X5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="42.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.18"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="8.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.09"/>
